--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -73,15 +73,18 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="34" customWidth="1"/>
+    <col min="14" max="14" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -92,56 +95,135 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t>Ссылка на владельца</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t>Плательщик</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t>Период / сбор</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>Тип сбора</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t>Начислено, ILS</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t>Оплачено, ILS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>Долг / переплата, ILS</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t>Дата оплаты</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t>Способ оплаты</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t>№ квитанции</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="M1" t="inlineStr" s="1">
         <is>
           <t>Документ</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="N1" t="inlineStr" s="1">
         <is>
           <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="0">
+        <is>
+          <t>דירה 15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-10</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F2" s="0">
+        <v>1000</v>
+      </c>
+      <c r="G2" s="0">
+        <v>1030</v>
+      </c>
+      <c r="H2" s="0">
+        <v>-30</v>
+      </c>
+      <c r="I2" t="inlineStr" s="0">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="0">
+        <is>
+          <t>אישור Telegram</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="0">
+        <is>
+          <t>переплата</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="0">
+        <is>
+          <t>Закрыто с января по октябрь 2026 включительно; переплата 30 ILS.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:N2"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -223,7 +223,71 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>16</v>
+      </c>
+      <c r="B3" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="0">
+        <is>
+          <t>דירה 16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F3" s="0">
+        <v>1200</v>
+      </c>
+      <c r="G3" s="0">
+        <v>1200</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr" s="0">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="0">
+        <is>
+          <t>העברה בנקאית</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="0">
+        <is>
+          <t>895-96218/58; אסמכתא 10806</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-08-06-apartment-16-vaad-fee-1200.jpg</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr" s="0">
+        <is>
+          <t>За 2026 год полностью: 12 × 100 ILS; дата валютирования 2026-08-07.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N3"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -287,7 +287,71 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="0">
+        <is>
+          <t>דירה 2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F4" s="0">
+        <v>600</v>
+      </c>
+      <c r="G4" s="0">
+        <v>600</v>
+      </c>
+      <c r="H4" s="0">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-02-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--июнь 2026: 6 × 100 ILS; подтверждено квитанцией.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N4"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -351,7 +351,71 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 3</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>דירה 3</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F5" s="0">
+        <v>600</v>
+      </c>
+      <c r="G5" s="0">
+        <v>600</v>
+      </c>
+      <c r="H5" s="0">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-03-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t>Оплата за январь--июнь 2026: 6 × 100 ILS; подтверждено квитанцией.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N5"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -415,7 +415,71 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>4</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 4</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>דירה 4</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>2026-01--2026-04</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F6" s="0">
+        <v>400</v>
+      </c>
+      <c r="G6" s="0">
+        <v>400</v>
+      </c>
+      <c r="H6" s="0">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+      <c r="L6" s="0" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-04-vaad-fee-400.jpg</t>
+        </is>
+      </c>
+      <c r="N6" s="0" t="inlineStr">
+        <is>
+          <t>Оплата за январь--апрель 2026: 4 × 100 ILS; наличными, квитанция № 3/26.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N6"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -479,7 +479,71 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>5</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 5</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>דירה 5</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>2026-01--2026-05</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F7" s="0">
+        <v>500</v>
+      </c>
+      <c r="G7" s="0">
+        <v>500</v>
+      </c>
+      <c r="H7" s="0">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>4/26</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-05-vaad-fee-500.jpg</t>
+        </is>
+      </c>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t>Оплата за январь--май 2026: 5 × 100 ILS; наличными, квитанция № 4/26.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
+  <autoFilter ref="A1:N7"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -543,7 +543,71 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t>דירה 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t>2026-07--2026-08</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F8" s="0">
+        <v>200</v>
+      </c>
+      <c r="G8" s="0">
+        <v>200</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr" s="0">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr" s="0">
+        <is>
+          <t>העברה בנקאית</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr" s="0">
+        <is>
+          <t>אסמכתא 4763-2073-2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-08-13-apartment-01-vaad-fee-200.jpg</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за июль--август 2026: 2 × 100 ILS; банковский перевод, асмכתא 4763-2073-2.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N7"/>
+  <autoFilter ref="A1:N8"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -607,7 +607,71 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t>דירה 6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F9" s="0">
+        <v>600</v>
+      </c>
+      <c r="G9" s="0">
+        <v>600</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr" s="0">
+        <is>
+          <t>5/26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-06-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--июнь 2026: 6 × 100 ILS; наличными, квитанция № 5/26.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N9"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -671,7 +671,199 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t>דירה 7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F10" s="0">
+        <v>1200</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1200</v>
+      </c>
+      <c r="H10" s="0">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr" s="0">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-07-vaad-fee-1200.jpg</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--декабрь 2026: 12 × 100 ILS; наличными, квитанция № 6/26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="0">
+        <is>
+          <t>דירה 8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F11" s="0">
+        <v>500</v>
+      </c>
+      <c r="G11" s="0">
+        <v>500</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr" s="0">
+        <is>
+          <t>7/26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-08-vaad-fee-500.jpg</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--май 2026: 5 × 100 ILS; наличными, квитанция № 7/26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t>owners.xlsx / דירה 9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t>דירה 9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F12" s="0">
+        <v>600</v>
+      </c>
+      <c r="G12" s="0">
+        <v>600</v>
+      </c>
+      <c r="H12" s="0">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr" s="0">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-09-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--июнь 2026: 6 × 100 ILS; наличными, квитанция № 8/26.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N12"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -268,7 +268,7 @@
       </c>
       <c r="K3" t="inlineStr" s="0">
         <is>
-          <t>895-96218/58; אסמכתא 10806</t>
+          <t>895-96218/58; אסמכתא 10806; 16/26</t>
         </is>
       </c>
       <c r="L3" t="inlineStr" s="0">
@@ -278,12 +278,12 @@
       </c>
       <c r="M3" t="inlineStr" s="0">
         <is>
-          <t>documents/payments/2026-08-06-apartment-16-vaad-fee-1200.jpg</t>
+          <t>documents/payments/2026-08-06-apartment-16-vaad-fee-1200.jpg; documents/payments/2026-08-06-apartment-16-vaad-fee-1200-receipt.jpg</t>
         </is>
       </c>
       <c r="N3" t="inlineStr" s="0">
         <is>
-          <t>За 2026 год полностью: 12 × 100 ILS; дата валютирования 2026-08-07.</t>
+          <t>За 2026 год полностью: 12 × 100 ILS; дата валютирования 2026-08-07. Квитанция № 16/26 от 2026-08-06.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="K8" t="inlineStr" s="0">
         <is>
-          <t>אסמכתא 4763-2073-2</t>
+          <t>אסמכתא 4763-2073-2; 17/26</t>
         </is>
       </c>
       <c r="L8" t="inlineStr" s="0">
@@ -598,12 +598,12 @@
       </c>
       <c r="M8" t="inlineStr" s="0">
         <is>
-          <t>documents/payments/2026-08-13-apartment-01-vaad-fee-200.jpg</t>
+          <t>documents/payments/2026-08-13-apartment-01-vaad-fee-200.jpg; documents/payments/2026-08-13-apartment-01-vaad-fee-200-receipt.jpg</t>
         </is>
       </c>
       <c r="N8" t="inlineStr" s="0">
         <is>
-          <t>Оплата за июль--август 2026: 2 × 100 ILS; банковский перевод, асмכתא 4763-2073-2.</t>
+          <t>Оплата за июль--август 2026: 2 × 100 ILS; банковский перевод, асмכתא 4763-2073-2. Квитанция № 17/26 от 2026-08-13.</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,461 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="0">
+        <is>
+          <t xml:space="preserve">owners.xlsx / דירה 10</t>
+        </is>
+      </c>
+      <c r="C13" s="0">
+        <is>
+          <t>דירה 10</t>
+        </is>
+      </c>
+      <c r="D13" s="0">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E13" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F13" s="0">
+        <v>600</v>
+      </c>
+      <c r="G13" s="0">
+        <v>600</v>
+      </c>
+      <c r="H13" s="0">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J13" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K13" s="0">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+      <c r="L13" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M13" s="0">
+        <is>
+          <t xml:space="preserve">documents/payments/2026-06-04-apartment-10-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N13" s="0">
+        <is>
+          <t xml:space="preserve">Оплата за январь--июнь 2026: 6 × 100 ILS; наличными, квитанция № 10/26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="0">
+        <is>
+          <t xml:space="preserve">owners.xlsx / דירה 11</t>
+        </is>
+      </c>
+      <c r="C14" s="0">
+        <is>
+          <t>דירה 11</t>
+        </is>
+      </c>
+      <c r="D14" s="0">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E14" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F14" s="0">
+        <v>600</v>
+      </c>
+      <c r="G14" s="0">
+        <v>600</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J14" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K14" s="0">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+      <c r="L14" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M14" s="0">
+        <is>
+          <t xml:space="preserve">documents/payments/2026-06-04-apartment-11-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N14" s="0">
+        <is>
+          <t xml:space="preserve">Оплата за январь--июнь 2026: 6 × 100 ILS; наличными, квитанция № 10/26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">owners.xlsx / דירה 17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t>דירה 17</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F15" s="0">
+        <v>600</v>
+      </c>
+      <c r="G15" s="0">
+        <v>600</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr" s="0">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-17-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--июнь 2026: 6 × 100 ILS; наличными, квитанция № 11/26. Номер совпадает с квитанцией квартиры 11 — требуется сверка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>18</v>
+      </c>
+      <c r="B16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">owners.xlsx / דירה 18</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="0">
+        <is>
+          <t>דירה 18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F16" s="0">
+        <v>1200</v>
+      </c>
+      <c r="G16" s="0">
+        <v>1200</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr" s="0">
+        <is>
+          <t>12/26</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-18-vaad-fee-1200.jpg</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--декабрь 2026: 12 × 100 ILS; наличными, квитанция № 12/26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>19</v>
+      </c>
+      <c r="B17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">owners.xlsx / דירה 19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="0">
+        <is>
+          <t>דירה 19</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="0">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="0">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F17" s="0">
+        <v>600</v>
+      </c>
+      <c r="G17" s="0">
+        <v>600</v>
+      </c>
+      <c r="H17" s="0">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr" s="0">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr" s="0">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr" s="0">
+        <is>
+          <t>13/26</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr" s="0">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr" s="0">
+        <is>
+          <t>documents/payments/2026-06-04-apartment-19-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr" s="0">
+        <is>
+          <t>Оплата за январь--июнь 2026: 6 × 100 ILS; наличными, квитанция № 13/26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>14</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 14</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>דירה 14</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F18" s="0">
+        <v>600</v>
+      </c>
+      <c r="G18" s="0">
+        <v>600</v>
+      </c>
+      <c r="H18" s="0">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>14/26</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t>documents/payments/2026-06-06-apartment-14-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N18" s="0" t="inlineStr">
+        <is>
+          <t>Наличные; оплата за январь--июнь 2026: 6 × 100 ILS. Квитанция № 14/26 от 2026-06-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>1</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 1</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>דירה 1</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>2026-01--2026-06</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F19" s="0">
+        <v>600</v>
+      </c>
+      <c r="G19" s="0">
+        <v>600</v>
+      </c>
+      <c r="H19" s="0">
+        <v>0</v>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>15/26</t>
+        </is>
+      </c>
+      <c r="L19" s="0" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M19" s="0" t="inlineStr">
+        <is>
+          <t>documents/payments/2026-06-08-apartment-01-vaad-fee-600.jpg</t>
+        </is>
+      </c>
+      <c r="N19" s="0" t="inlineStr">
+        <is>
+          <t>Наличные; оплата за январь--июнь 2026: 6 × 100 ILS. Квитанция № 15/26 от 2026-06-08.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N12"/>
+  <autoFilter ref="A1:N19"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -1317,6 +1317,78 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>לואי סאלח</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-01--2026-12</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>העברה בנקאית (ONE ZERO)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>אסמכתא 1-25-22718524</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>documents/payments/2026-09-03-apartment-20-vaad-fee-1200.jpg</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>За 2026 год полностью: 12 × 100 ILS. Оплата подтверждена пользователем.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N19"/>
 </worksheet>
